--- a/RIC_FINAL_EVIDENCE_AND_DIMENSIONS_20260825_101657.xlsx
+++ b/RIC_FINAL_EVIDENCE_AND_DIMENSIONS_20260825_101657.xlsx
@@ -3620,6 +3620,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
